--- a/output/casestudy_20260823.xlsx
+++ b/output/casestudy_20260823.xlsx
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>10.79699820000678</v>
+        <v>11.1113060999196</v>
       </c>
     </row>
     <row r="3">
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>10.68681040010415</v>
+        <v>10.99903279996943</v>
       </c>
     </row>
     <row r="4">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>11.01032470003702</v>
+        <v>11.27688040002249</v>
       </c>
     </row>
     <row r="5">
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>11.14911939995363</v>
+        <v>11.69287499994971</v>
       </c>
     </row>
     <row r="6">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>11.29921550001018</v>
+        <v>11.76315640006214</v>
       </c>
     </row>
     <row r="7">
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>11.36150270001963</v>
+        <v>11.79748900001869</v>
       </c>
     </row>
   </sheetData>
@@ -7537,7 +7537,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>10.8 초</t>
+          <t>11.1 초</t>
         </is>
       </c>
     </row>
@@ -7549,7 +7549,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>10.7 초</t>
+          <t>11.0 초</t>
         </is>
       </c>
     </row>
@@ -7561,7 +7561,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>11.0 초</t>
+          <t>11.3 초</t>
         </is>
       </c>
     </row>
@@ -7573,7 +7573,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>11.1 초</t>
+          <t>11.7 초</t>
         </is>
       </c>
     </row>
@@ -7585,7 +7585,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>11.3 초</t>
+          <t>11.8 초</t>
         </is>
       </c>
     </row>
@@ -7597,7 +7597,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>11.4 초</t>
+          <t>11.8 초</t>
         </is>
       </c>
     </row>
@@ -7609,7 +7609,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>68.1 초</t>
+          <t>70.5 초</t>
         </is>
       </c>
     </row>
@@ -7887,7 +7887,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ESS 차익거래 수익은 매 평일 한 사이클을 온전히 돌렸을 때의 잠재값이며 피크저감 절감액에 합산하지 않았습니다. 피크컷 디스패치가 이미 일부를 실현하고 있어 합산하면 이중 계산이 됩니다.</t>
+          <t>ESS 차익거래 수익은 매 평일 한 사이클을 온전히 돌렸을 때의 잠재값이며 피크저감 절감액에 합산하지 않았습니다. 그 운전을 하려면 그날 피크에 쓸 몫을 남기는 예비 규칙이 필요한데 아직 정하지 않았고, 예비 없이 돌리면 피크를 못 깎아 회수기간이 오히려 나빠집니다. 사이클이 수십 배로 늘어나는 열화도 반영하지 않았습니다.</t>
         </is>
       </c>
     </row>
